--- a/zhul-erp-backend/src/test/resources/document-template/fouwell-pi-v2.xlsx
+++ b/zhul-erp-backend/src/test/resources/document-template/fouwell-pi-v2.xlsx
@@ -2333,7 +2333,11 @@
       </c>
     </row>
     <row r="14" customFormat="1" s="3">
-      <c r="B14" s="37" t="n"/>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>${fee.no}</t>
+        </is>
+      </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
           <t>${fee.name}</t>
